--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.43448249326378</v>
+        <v>2.020603405155364</v>
       </c>
       <c r="D2" t="n">
-        <v>12.24136032499696</v>
+        <v>1.989221052812005</v>
       </c>
       <c r="E2" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F2" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.203494342285693</v>
+        <v>1.008067830621425</v>
       </c>
       <c r="D3" t="n">
-        <v>6.007991860355144</v>
+        <v>0.9762986773077109</v>
       </c>
       <c r="E3" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F3" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.55155448072706</v>
+        <v>3.827127603118148</v>
       </c>
       <c r="D4" t="n">
-        <v>26.4040090588941</v>
+        <v>4.290651472070292</v>
       </c>
       <c r="E4" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F4" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.00938793600939</v>
+        <v>2.926525539601526</v>
       </c>
       <c r="D5" t="n">
-        <v>18.17663926667098</v>
+        <v>2.953703880834034</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F5" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4.516148801800044</v>
+        <v>0.7338741802925073</v>
       </c>
       <c r="D6" t="n">
-        <v>8.346569403807012</v>
+        <v>1.356317528118639</v>
       </c>
       <c r="E6" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F6" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.87485690787999</v>
+        <v>3.229664247530498</v>
       </c>
       <c r="D7" t="n">
-        <v>19.85081497863025</v>
+        <v>3.225757434027416</v>
       </c>
       <c r="E7" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F7" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.83259234742246</v>
+        <v>5.172796256456149</v>
       </c>
       <c r="D8" t="n">
-        <v>35.77864917440916</v>
+        <v>5.814030490841489</v>
       </c>
       <c r="E8" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F8" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.4609735228871</v>
+        <v>5.599908197469154</v>
       </c>
       <c r="D9" t="n">
-        <v>43.74162294669053</v>
+        <v>7.108013728837211</v>
       </c>
       <c r="E9" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F9" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.48001248439178</v>
+        <v>4.628002028713664</v>
       </c>
       <c r="D10" t="n">
-        <v>35.38839845637256</v>
+        <v>5.75061474916054</v>
       </c>
       <c r="E10" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F10" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9.107505031828174</v>
+        <v>1.479969567672078</v>
       </c>
       <c r="D11" t="n">
-        <v>22.44622635065294</v>
+        <v>3.647511781981103</v>
       </c>
       <c r="E11" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F11" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.4787373002425</v>
+        <v>5.440294811289406</v>
       </c>
       <c r="D12" t="n">
-        <v>26.2132974360254</v>
+        <v>4.259660833354128</v>
       </c>
       <c r="E12" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F12" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>8.689880509055248</v>
+        <v>1.412105582721478</v>
       </c>
       <c r="D13" t="n">
-        <v>27.61632292759465</v>
+        <v>4.487652475734131</v>
       </c>
       <c r="E13" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F13" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.17377079758815</v>
+        <v>3.440737754608074</v>
       </c>
       <c r="D14" t="n">
-        <v>35.85219028949597</v>
+        <v>5.825980922043095</v>
       </c>
       <c r="E14" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F14" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20.61531894488458</v>
+        <v>3.349989328543744</v>
       </c>
       <c r="D15" t="n">
-        <v>37.2904186947112</v>
+        <v>6.05969303789057</v>
       </c>
       <c r="E15" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F15" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.56312504887753</v>
+        <v>6.104007820442599</v>
       </c>
       <c r="D16" t="n">
-        <v>10.96445692360281</v>
+        <v>1.781724250085457</v>
       </c>
       <c r="E16" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F16" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>21.69614460457675</v>
+        <v>3.525623498243722</v>
       </c>
       <c r="D17" t="n">
-        <v>4.344028195400768</v>
+        <v>0.7059045817526248</v>
       </c>
       <c r="E17" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F17" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>15.90422725077972</v>
+        <v>2.584436928251705</v>
       </c>
       <c r="D18" t="n">
-        <v>5.848603589799659</v>
+        <v>0.9503980833424446</v>
       </c>
       <c r="E18" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F18" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>16.37359261466801</v>
+        <v>2.660708799883552</v>
       </c>
       <c r="D19" t="n">
-        <v>18.78042800106308</v>
+        <v>3.051819550172751</v>
       </c>
       <c r="E19" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F19" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>7.189968930183627</v>
+        <v>1.16836995115484</v>
       </c>
       <c r="D20" t="n">
-        <v>18.52700731364891</v>
+        <v>3.010638688467947</v>
       </c>
       <c r="E20" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F20" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>13.72953021774598</v>
+        <v>2.231048660383722</v>
       </c>
       <c r="D21" t="n">
-        <v>8.112318996820386</v>
+        <v>1.318251836983313</v>
       </c>
       <c r="E21" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F21" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>15.31389842936686</v>
+        <v>2.488508494772115</v>
       </c>
       <c r="D22" t="n">
-        <v>1.755186836779376</v>
+        <v>0.2852178609766486</v>
       </c>
       <c r="E22" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F22" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>13.89953459389169</v>
+        <v>2.2586743715074</v>
       </c>
       <c r="D23" t="n">
-        <v>9.576409992140203</v>
+        <v>1.556166623722783</v>
       </c>
       <c r="E23" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F23" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>18.22107877986311</v>
+        <v>2.960925301727756</v>
       </c>
       <c r="D24" t="n">
-        <v>8.447775479782543</v>
+        <v>1.372763515464663</v>
       </c>
       <c r="E24" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F24" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>20.56860719739711</v>
+        <v>3.34239866957703</v>
       </c>
       <c r="D25" t="n">
-        <v>18.04618150170953</v>
+        <v>2.932504494027799</v>
       </c>
       <c r="E25" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F25" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>15.31973365790698</v>
+        <v>2.489456719409885</v>
       </c>
       <c r="D26" t="n">
-        <v>16.90605504858594</v>
+        <v>2.747233945395216</v>
       </c>
       <c r="E26" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F26" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>33.55869562045215</v>
+        <v>5.453288038323475</v>
       </c>
       <c r="D27" t="n">
-        <v>28.6794230885904</v>
+        <v>4.66040625189594</v>
       </c>
       <c r="E27" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F27" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>30.92637393398023</v>
+        <v>5.025535764271788</v>
       </c>
       <c r="D28" t="n">
-        <v>30.23577955973078</v>
+        <v>4.913314178456252</v>
       </c>
       <c r="E28" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F28" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>50.58813118037949</v>
+        <v>8.220571316811668</v>
       </c>
       <c r="D29" t="n">
-        <v>34.73800496816172</v>
+        <v>5.644925807326279</v>
       </c>
       <c r="E29" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F29" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>25.2703346700677</v>
+        <v>4.106429383886002</v>
       </c>
       <c r="D30" t="n">
-        <v>25.11503873471806</v>
+        <v>4.081193794391685</v>
       </c>
       <c r="E30" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F30" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>45.18410638068206</v>
+        <v>7.342417286860835</v>
       </c>
       <c r="D31" t="n">
-        <v>45.96419790886736</v>
+        <v>7.469182160190947</v>
       </c>
       <c r="E31" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F31" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>38.87911390020987</v>
+        <v>6.317856008784105</v>
       </c>
       <c r="D32" t="n">
-        <v>7.587073940122771</v>
+        <v>1.23289951526995</v>
       </c>
       <c r="E32" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F32" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>67.74171868887007</v>
+        <v>11.00802928694139</v>
       </c>
       <c r="D33" t="n">
-        <v>25.67039217211579</v>
+        <v>4.171438727968815</v>
       </c>
       <c r="E33" t="n">
-        <v>13.77055047612507</v>
+        <v>2.237714452370324</v>
       </c>
       <c r="F33" t="n">
-        <v>12.04820188454853</v>
+        <v>1.957832806239136</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
